--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2366,7 +2366,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46238.49007915509</v>
+        <v>46284.150090462965</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
